--- a/КартаMQTT.xlsx
+++ b/КартаMQTT.xlsx
@@ -97,10 +97,10 @@
     <t>SlaveID=1, Reg=769</t>
   </si>
   <si>
-    <t>SlaveID=1, Reg=770</t>
-  </si>
-  <si>
     <t>JSON</t>
+  </si>
+  <si>
+    <t>SlaveID=1, Reg=768</t>
   </si>
 </sst>
 </file>
@@ -575,10 +575,10 @@
         <v>25</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
@@ -616,10 +616,10 @@
         <v>25</v>
       </c>
       <c r="L3" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M3" s="3" t="s">
         <v>27</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
